--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2F97C5-D8F6-47AD-8B71-67C8B721C97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C377F496-6AB3-47D0-BDE7-8CBB54EF62FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
   <si>
     <t>ITEM</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>STATE CATEGORIES (URBAN, RURAL, ETC), ESSOS</t>
+  </si>
+  <si>
+    <t>BRA DONE</t>
   </si>
 </sst>
 </file>
@@ -1729,12 +1732,14 @@
         <v>87</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C71" s="3">
         <v>2</v>
       </c>
-      <c r="D71" s="6"/>
+      <c r="D71" s="6" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C377F496-6AB3-47D0-BDE7-8CBB54EF62FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E2DA4E-A7BC-4D8A-8EAB-547048C8DB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
   <si>
     <t>ITEM</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>BRA DONE</t>
+  </si>
+  <si>
+    <t>RE-ADD UNIT MODELS IN A CLEAN WAY</t>
+  </si>
+  <si>
+    <t>In a way that doesnt add 6K bugs Xd</t>
   </si>
 </sst>
 </file>
@@ -399,7 +405,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -851,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1753,13 +1794,38 @@
       </c>
       <c r="D72" s="6"/>
     </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D72">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B1:B58 B73:B1048576">
+  <conditionalFormatting sqref="B1:B58 B74:B1048576">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>"IN PROGRESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>"NOT STARTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+      <formula>"FINISHED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B60">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1770,7 +1836,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59:B60">
+  <conditionalFormatting sqref="B61">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1781,7 +1847,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
+  <conditionalFormatting sqref="B62:B70">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1792,7 +1858,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B62:B70">
+  <conditionalFormatting sqref="B71:B72">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1803,7 +1869,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B71:B72">
+  <conditionalFormatting sqref="B73">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E2DA4E-A7BC-4D8A-8EAB-547048C8DB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E136191E-2E62-4FBF-98E4-E061352B7651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -285,9 +285,6 @@
     <t>REMOVE 100+ EMPTY STATES</t>
   </si>
   <si>
-    <t>SEASON 1 &amp; 2 DONE</t>
-  </si>
-  <si>
     <t>ONLY CRO &amp; NWA HAVE CUSTOM ADVISORS (CODE ONLY, GENERIC GFX), REST GENERIC</t>
   </si>
   <si>
@@ -307,6 +304,9 @@
   </si>
   <si>
     <t>In a way that doesnt add 6K bugs Xd</t>
+  </si>
+  <si>
+    <t>SEASON 1-4 DONE</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1281,7 @@
         <v>58</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C32" s="3">
         <v>2</v>
@@ -1339,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>2</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1666,7 +1666,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>31</v>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>43</v>
@@ -1779,12 +1779,12 @@
         <v>2</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>31</v>
@@ -1796,16 +1796,16 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="3">
-        <v>1</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E136191E-2E62-4FBF-98E4-E061352B7651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19E6587-9FEB-41D6-8E4C-823036A228B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
   <si>
     <t>ITEM</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>SEASON 1-4 DONE</t>
+  </si>
+  <si>
+    <t>Make S3 and S4 events add tension</t>
   </si>
 </sst>
 </file>
@@ -892,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1806,6 +1809,11 @@
       </c>
       <c r="D73" s="6" t="s">
         <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F19E6587-9FEB-41D6-8E4C-823036A228B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C68B46-8D14-49DE-9924-D3C8919BA8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
   <si>
     <t>ITEM</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Make S3 and S4 events add tension</t>
+  </si>
+  <si>
+    <t>Coring States Decision</t>
   </si>
 </sst>
 </file>
@@ -895,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1814,6 +1817,11 @@
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C68B46-8D14-49DE-9924-D3C8919BA8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E2DDD-C86C-4D6D-BD12-1BBCE1CEB01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="97">
   <si>
     <t>ITEM</t>
   </si>
@@ -313,6 +313,12 @@
   </si>
   <si>
     <t>Coring States Decision</t>
+  </si>
+  <si>
+    <t>Add Vanilla Stability Events</t>
+  </si>
+  <si>
+    <t>Add Vanilla Election Events</t>
   </si>
 </sst>
 </file>
@@ -411,7 +417,112 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -898,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1535,7 +1646,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C52" s="3">
         <v>2</v>
@@ -1723,7 +1834,7 @@
         <v>74</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C67" s="3">
         <v>2</v>
@@ -1779,7 +1890,7 @@
         <v>86</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C71" s="3">
         <v>2</v>
@@ -1815,14 +1926,44 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="6" t="s">
         <v>93</v>
       </c>
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="6"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="6" t="s">
         <v>94</v>
       </c>
+      <c r="B75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="6"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="6"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -1830,7 +1971,40 @@
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="B1:B58 B74:B1048576">
+  <conditionalFormatting sqref="B1:B58 B75 B78:B1048576">
+    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
+      <formula>"IN PROGRESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
+      <formula>"NOT STARTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="27" operator="equal">
+      <formula>"FINISHED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B60">
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+      <formula>"IN PROGRESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+      <formula>"NOT STARTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
+      <formula>"FINISHED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="cellIs" dxfId="20" priority="19" operator="equal">
+      <formula>"IN PROGRESS"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+      <formula>"NOT STARTED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
+      <formula>"FINISHED"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62:B70">
     <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1841,7 +2015,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59:B60">
+  <conditionalFormatting sqref="B71:B72">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1852,7 +2026,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
+  <conditionalFormatting sqref="B73">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1863,7 +2037,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B62:B70">
+  <conditionalFormatting sqref="B74">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1874,7 +2048,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B71:B72">
+  <conditionalFormatting sqref="B76">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>
@@ -1885,7 +2059,7 @@
       <formula>"FINISHED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B73">
+  <conditionalFormatting sqref="B77">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"IN PROGRESS"</formula>
     </cfRule>

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E2DDD-C86C-4D6D-BD12-1BBCE1CEB01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F9D973-308C-4558-B9A0-DF2B539F1035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="98">
   <si>
     <t>ITEM</t>
   </si>
@@ -303,9 +303,6 @@
     <t>RE-ADD UNIT MODELS IN A CLEAN WAY</t>
   </si>
   <si>
-    <t>In a way that doesnt add 6K bugs Xd</t>
-  </si>
-  <si>
     <t>SEASON 1-4 DONE</t>
   </si>
   <si>
@@ -319,6 +316,12 @@
   </si>
   <si>
     <t>Add Vanilla Election Events</t>
+  </si>
+  <si>
+    <t>Readded Ships, and most Buildings Succesfully</t>
+  </si>
+  <si>
+    <t>Add option to Limit Event Spam</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1456,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1848,7 +1851,7 @@
         <v>76</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C68" s="3">
         <v>2</v>
@@ -1916,18 +1919,18 @@
         <v>90</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C73" s="3">
         <v>1</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>31</v>
@@ -1937,7 +1940,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -1947,7 +1950,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>31</v>
@@ -1957,13 +1960,21 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="6"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F9D973-308C-4558-B9A0-DF2B539F1035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7344E6-7F06-498F-8C84-F5BB77B2FA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="99">
   <si>
     <t>ITEM</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Add option to Limit Event Spam</t>
+  </si>
+  <si>
+    <t>Add different models for Asian/Arab/Dorne/Dothraki</t>
   </si>
 </sst>
 </file>
@@ -1012,10 +1015,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="100.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -1976,6 +1979,11 @@
       <c r="C78" s="3"/>
       <c r="D78" s="6"/>
     </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D72">

--- a/00_Checklist.xlsx
+++ b/00_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paradox Interactive\Hearts of Iron IV\mod\FAB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7344E6-7F06-498F-8C84-F5BB77B2FA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19C8162-CFF0-432E-A768-0EF2CDE1633A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,9 +303,6 @@
     <t>RE-ADD UNIT MODELS IN A CLEAN WAY</t>
   </si>
   <si>
-    <t>SEASON 1-4 DONE</t>
-  </si>
-  <si>
     <t>Make S3 and S4 events add tension</t>
   </si>
   <si>
@@ -325,6 +322,9 @@
   </si>
   <si>
     <t>Add different models for Asian/Arab/Dorne/Dothraki</t>
+  </si>
+  <si>
+    <t>SEASON 1-5 DONE</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
         <v>66</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C61" s="3">
         <v>2</v>
@@ -1780,7 +1780,7 @@
         <v>67</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C62" s="3">
         <v>2</v>
@@ -1928,12 +1928,12 @@
         <v>1</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>31</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>31</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>31</v>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
